--- a/outputs/Broke System.functional_locations.xlsx
+++ b/outputs/Broke System.functional_locations.xlsx
@@ -314,37 +314,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Sinan Aydın</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Alanın formatı ve karakter sayısı hakkında bilgi.
-CHAR herhangi bir karakter girilebileceği
-NUM sadece nümerik değer girilebileceği
-DATE tarih formatında alan girilebileceğini,
-gösterir...
-</t>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Alanın doldurulmasının zorunlu olup, olmadığını gösterir.
-</t>
-      </text>
-    </comment>
-    <comment ref="A6" authorId="0" shapeId="0">
-      <text>
-        <t>Bu alan işaretli olduğunda, alan için değer, seçim kutusundaki değerlerden seçilir.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -646,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.42578125" customWidth="1" min="1" max="1"/>
@@ -1474,7 +1443,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1598,7 +1567,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1679,6 +1648,2776 @@
         </is>
       </c>
       <c r="S16" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L006</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0060</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>35-24L006 BROKE CVYR 3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>35-24L007 SLABBING PLPR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L008</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>35-24L008 WINDER PLPR</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L009</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0090</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>35-24L009 BROKE ROLL PLPR</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L010</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>35-24L010 BROKE SCRN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24L011</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>35-24L011 BROKE CVYR 1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P501</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>35-24P501 COUCH PIT PMP</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P502</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>35-24P502 COUCH PIT PMP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P503</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0140</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>35-24P503 PRESS PLPR GRBX OL PMP</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P504</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>35-24P504 BROKE CONV 1 PMP</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P505</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>35-24P505 SIZE PRESS PLPR PMP</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P506</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0170</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>35-24P506 REEL PLPR PMP</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P507</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0180</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>35-24P507 BROKE CONV 3 PMP</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P508</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0190</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>35-24P508 SLABBING PLPR PMP</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P509</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>35-24P509 GB OL PMP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P510</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0210</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>35-24P510 BROKE PMP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P511</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0220</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>35-24P511 BROKE COLL PMP 60L/S</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P512</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>35-24P512 BROKE PMP</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P513</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>35-24P513 BR1 BROKE PMP</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P514</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>35-24P514 BROKE STOR PMP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P515</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0260</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>35-24P515 THICKENED BROKE PMP</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P516</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>35-24P516 BROKE FLTRT PMP</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P517</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0280</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>35-24P517 BROKE DOS PMP</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P518</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0290</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>35-24P518 BROKE REJ PMP</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P519</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>35-24P519 BROKE ROLL PLPR PMP</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24P520</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>35-24P520 REEL PULPR PMP</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T601</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>35-24T601 COUCH PIT TNK 176M3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T602</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>35-24T602 BROKE STOR TWR 4000M3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T603</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>35-24T603 BROKE COLLECTION TNK 40M3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T604</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>35-24T604 BROKE FLTRT TNK 40M3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T605</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>35-24T605 THICKENED BROKE TNK 70M3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T606</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0370</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>35-24T606 BROKE REJ TNK 15M3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24T607</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0380</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>35-24T607 BROKE DOS TNK 35M3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24ES-508</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>35-24ES-508 WINDER AREA EMERG STOP</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24ES-601</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>35-24ES-601 UTM E-STOP</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24ES-662</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0410</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>35-24ES-662 BROKE THICKENER EMRG STOP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24ES-663</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0420</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>35-24ES-663 BROKE THICKENER E-STOP</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24ES-683</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>35-24ES-683 BROK ROLL PLPR EMRG STOP</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-501</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>35-24HI-501 HI VLV POSITION IND</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-503</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>35-24HI-503 WNDR PLPR SHW S5 S6 IND</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-516</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0460</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>35-24HI-516 WNDR PLPR SHW S1 S2 IND</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-529</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>35-24HI-529 SLBG PLPR SHW S1 IND</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-532</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0480</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>35-24HI-532 HIGH IND INSTR</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-534</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0490</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>35-24HI-534 HIGH IND</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-552</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>35-24HI-552 REEL PLPR TAIL SHW ST IND</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>MECH</t>
         </is>
@@ -1694,6 +4433,5 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/outputs/Broke System.functional_locations.xlsx
+++ b/outputs/Broke System.functional_locations.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.42578125" customWidth="1" min="1" max="1"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>35-24P511 BROKE COLL PMP 60L/S</t>
+          <t>35-24P511 BROKE COLLECTION PMP</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>35-24P512 BROKE PMP</t>
+          <t>35-24P512 BROKE SYS PMP</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>35-24P520 REEL PULPR PMP</t>
+          <t>35-24P520 REEL PLPR PMP</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>35-24T602 BROKE STOR TWR 4000M3</t>
+          <t>35-24T602 BROKE STOR TWR TNK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>35-24ES-508 WINDER AREA EMERG STOP</t>
+          <t>35-24ES-508 WINDER AREA EMRG STOP</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>35-24HI-501 HI VLV POSITION IND</t>
+          <t>35-24HI-501 HI HND IND</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4045,11 +4045,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>5001</t>
@@ -4063,11 +4058,6 @@
       <c r="R55" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4208,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>35-24HI-529 SLBG PLPR SHW S1 IND</t>
+          <t>35-24HI-529 SLABBING PLPR SHW S1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4418,6 +4408,7110 @@
         </is>
       </c>
       <c r="S61" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-555</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>35-24HI-555 REEL PLPR SHW S1 IND</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-572</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0520</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>35-24HI-572 HI WAF LVL IND</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-575</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>35-24HI-575 HIGH IND</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-580</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0540</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>35-24HI-580 PRESS PLPR SHW S1 IND</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-583</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0550</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>35-24HI-583 PRESS PLPR SHW S2 HI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-597</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0560</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>35-24HI-597 COUCH PIT SHW S1 IND</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-623</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0570</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>35-24HI-623 BROKE THICKENER LVL HI</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-633</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0580</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>35-24HI-633 BROKE THICKENER HI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-652</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0590</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>35-24HI-652 HIGH IND</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-653</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>35-24HI-653 REEL PLPR SHW S2 IND</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HI-654</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0610</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>35-24HI-654 PRESS PLPR SHW S3 IND</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-501</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>35-24HS-501 HS BROKE DIL VLV CTRL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-503</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>35-24HS-503 WNDR PLPR SHW S5 S6 HS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-509</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0640</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>35-24HS-509 WNDR PLPR START/STOP HS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-516</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>35-24HS-516 WNDR PLPR SHOWERS S1 S2 HS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-522</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>35-24HS-522 SLBG PLPR START STOP HS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-529</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0670</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>35-24HS-529 SLABBING PLPR SHW S1 HS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-532</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0680</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>35-24HS-532 HS SELECTOR SW</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-534</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0690</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>35-24HS-534 REEL PLPR SHW S3 HS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-542</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>35-24HS-542 REEL PLPR START/STOP HS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-552</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>35-24HS-552 REEL PLPR TAIL SHW START</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-555</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0720</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>35-24HS-555 HND SW BROKE SEL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-563</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>35-24HS-563 SIZE PRESS PLPR SHW ST/SP</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-572</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0740</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>35-24HS-572 SPPLPR SHWRS S1 TAIL HS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-575</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0750</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>35-24HS-575 HND SW</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-580</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0760</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>35-24HS-580 PRESS PLPR SHW S1 HS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-583</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0770</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>35-24HS-583 HND SW</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-585</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0780</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>35-24HS-585 PRESS PLPR START STOP</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-597</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0790</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>35-24HS-597 COUCH PIT SHW S1 HS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-626</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>35-24HS-626 BROKE THKR HS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-628</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>35-24HS-628 BROKE THICKENER HS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-629</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>35-24HS-629 BROKE THKR LOC/REMOTE SW</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-630</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>35-24HS-630 BROKE THICKENER JOG SW</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-652</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>35-24HS-652 HND SW STN</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-653</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>35-24HS-653 REEL PLPR SHW S2 HS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-654</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0860</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>35-24HS-654 PRESS PLPR SHW S3 HS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-664</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0870</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>35-24HS-664 COUCH PIT START STOP</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24HS-682</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0880</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>35-24HS-682 BROK ROLL PLPR START/STOP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-510</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0890</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>35-24KJ-510 WINDER PLPR START PB</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-511</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>35-24KJ-511 WNDR PLPR STOP PUSHBTN</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-523</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>35-24KJ-523 SLABBING PLPR START</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-524</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>35-24KJ-524 SLABBING PLPR STOP</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-543</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>35-24KJ-543 REEL PLPR START</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-544</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>35-24KJ-544 REEL PULPR STOP</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-564</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>35-24KJ-564 SIZE PRESS PLPR START</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-565</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>35-24KJ-565 SIZE PRESS PLPR STOP</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-589</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0970</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>35-24KJ-589 PRESS PLPR START</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-590</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0980</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>35-24KJ-590 PRESS PLPR STOP CMD</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-602</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0990</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>35-24KJ-602 COUCH PIT START</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-603</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>35-24KJ-603 COUCH PIT STOP</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-684</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>35-24KJ-684 BROK ROLL PLPR START</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-685</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>35-24KJ-685 BROK ROLL PLPR STOP</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-686</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>35-24KJ-686 BROKE THKR START SEQ</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-687</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>35-24KJ-687 BROKE THKR STOP SEQ</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-688</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>35-24KJ-688 BROKE SCRN START SEQ</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24KJ-689</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>35-24KJ-689 BROKE SCRNG STOP SEQ</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-541</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>35-24XS-541 REEL PLPR MCS SIG</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-562</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>35-24XS-562 SIZE PRESS PLPR MCS SIG</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-588</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>35-24XS-588 PRESS PLPR MCS SIGNAL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-600</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>35-24XS-600 COUCH PIT MCS SIGNALS</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-690</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>35-24XS-690 SLABBING PLPR MCS SIG</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-691</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>35-24XS-691 WNDR AREA MCS SIG</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24XS-692</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>35-24XS-692 BROK ROLL PLPR MCS SIG</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-008</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>35-24-008 WINDER PLPR WFL LN</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-010</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>35-24-010 WNDR PLPR RTR2 GRBX OL LN</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-012</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>35-24-012 WFL 15 PROC LN</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-016</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>35-24-016 WAF 250 HEADER LN</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-017</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>35-24-017 WAF 300 LN</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-024</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>35-24-024 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>35-24-026 WFL 15 GB OL LUB LN</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-028</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>35-24-028 WFL LN</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-030</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>35-24-030 WAF 250 HEADER LN</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-032</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>35-24-032 WAF 300 LN</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-042</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>35-24-042 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-045</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>35-24-045 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-048</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>35-24-048 GB OL WFL LN</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-050</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>35-24-050 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-052</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>35-24-052 WAF 300 DIST HDR LN</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-054</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>35-24-054 WAF 500 HEADER LN</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-056</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>35-24-056 WAF-350 BROKE HDR LN</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-061</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>35-24-061 WFL 15 PROC LN</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-063</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>35-24-063 WAF-250 BROKE LN</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-068</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>35-24-068 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-076</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>35-24-076 WFL LN 15 GB OL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-079</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>35-24-079 WFL 15 FL LN</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-080</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>35-24-080 WFL LN</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-083</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>35-24-083 WAF 300 HEADER LN</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-087</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>35-24-087 WAF 500 LN</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-088</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>35-24-088 WAF LN 300</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-089</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>35-24-089 WAF-300 LN</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-097</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>35-24-097 WFL LN 15</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-098</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>35-24-098 WAF LN 300</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-099</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>35-24-099 WFL LN BR1</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-102</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>35-24-102 WFL LN BR1</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-104</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>35-24-104 BROKE WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-105</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>35-24-105 WAF-300 PROC LN</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-106</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>35-24-106 WAF 500 BROKE LN</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-109</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>35-24-109 WAF 500 LN</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-112</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>35-24-112 WAF-400 APPROACH FL LN</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-115</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>35-24-115 WAF 250 COUCH PIT FD LN</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-117</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>35-24-117 PP-250 COUCH PIT LN</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-121</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>35-24-121 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-122</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>35-24-122 WFL LN BR1</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-123</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>35-24-123 WFL PROC LN DN15</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-125</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>35-24-125 WFL PROC LN</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-128</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>35-24-128 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-129</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>35-24-129 WFL LN BR1</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-136</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>35-24-136 WFL PROC LN</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-138</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>35-24-138 WFL LN</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-153</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>35-24-153 PROC LN WFL</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-157</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>35-24-157 PROC LN WFL</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-160</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>35-24-160 WFL PROC LN</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-163</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>35-24-163 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-167</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>35-24-167 PROC LN WFL DN15</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-171</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>35-24-171 PROC LN WFL</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-175</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>35-24-175 PROC LN WFL</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-185</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>35-24-185 WAF 150 LN</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-194</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>35-24-194 WFL 15 FLSH LN</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-195</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1690</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>35-24-195 WFL LN</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-203</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>35-24-203 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-213</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>35-24-213 WAF LN DN20</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-215</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>35-24-215 CLG WTR SEND LN</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-216</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>35-24-216 CLG WTR RTN LN</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-219</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>35-24-219 WFL LN DN15</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-24-224</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>35-24-224 WFL LN BR1</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-25-034</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>35-25-034 WAF LN 600</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1-35-25-072</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>5001-PM03-BR-BR1</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>NNNN-XXXX-AA-XXX-XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>35-25-072 WAF LN DN350 FM WHT WTR TNK</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
         <is>
           <t>MECH</t>
         </is>

--- a/outputs/Broke System.functional_locations.xlsx
+++ b/outputs/Broke System.functional_locations.xlsx
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>35-24P513 BR1 BROKE PMP</t>
+          <t>35-24P513 BR1 BROKE PMP 140L/S</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>35-24P514 BROKE STOR PMP</t>
+          <t>35-24P514 BROKE STOR TWR PMP</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>35-24T602 BROKE STOR TWR TNK</t>
+          <t>35-24T602 BROKE STOR TWR 4000M3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>35-24HI-501 HI HND IND</t>
+          <t>35-24HI-501 HI VLV POSITION IND</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4045,6 +4045,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>5001</t>
@@ -4058,6 +4063,11 @@
       <c r="R55" t="inlineStr">
         <is>
           <t>P01</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4094,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>35-24HI-503 WNDR PLPR SHW S5 S6 IND</t>
+          <t>35-24HI-503 WNDR PLPR SHW S5&amp;S6 IND</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4208,7 +4218,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>35-24HI-529 SLABBING PLPR SHW S1</t>
+          <t>35-24HI-529 SLABBING PLPR SHW S1 IND</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4270,7 +4280,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>35-24HI-532 HIGH IND INSTR</t>
+          <t>35-24HI-532 HIGH IND</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4436,7 +4446,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>35-24HI-555 REEL PLPR SHW S1 IND</t>
+          <t>35-24HI-555 REEL PLPR SHW S1 HI</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4498,7 +4508,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>35-24HI-572 HI WAF LVL IND</t>
+          <t>35-24HI-572 LVL HI INSTR</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4550,7 +4560,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>35-24HI-575 HIGH IND</t>
+          <t>35-24HI-575 HIGH IND INSTR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4912,7 +4922,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>35-24HI-652 HIGH IND</t>
+          <t>35-24HI-652 HIGH IND INST</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5088,7 +5098,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>35-24HS-501 HS BROKE DIL VLV CTRL</t>
+          <t>35-24HS-501 HND SW</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5101,11 +5111,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>5001</t>
@@ -5119,11 +5124,6 @@
       <c r="R73" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>35-24HS-529 SLABBING PLPR SHW S1 HS</t>
+          <t>35-24HS-529 SLBNG PLPR SHW S1 HS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>35-24HS-532 HS SELECTOR SW</t>
+          <t>35-24HS-532 HND SW</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>35-24HS-555 HND SW BROKE SEL</t>
+          <t>35-24HS-555 HND SW</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>35-24HS-575 HND SW</t>
+          <t>35-24HS-575 HND SW BROKE CONV 2</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>35-24HS-583 HND SW</t>
+          <t>35-24HS-583 HND SW BROKE DIST</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>35-24HS-629 BROKE THKR LOC/REMOTE SW</t>
+          <t>35-24HS-629 LOC/REMOTE SEL SW</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>35-24HS-652 HND SW STN</t>
+          <t>35-24HS-652 HND SW</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>35-24HS-664 COUCH PIT START STOP</t>
+          <t>35-24HS-664 COUCH PIT START STOP HS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>35-24HS-682 BROK ROLL PLPR START/STOP</t>
+          <t>35-24HS-682 BROK ROLL PLPR START STOP</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>35-24KJ-510 WINDER PLPR START PB</t>
+          <t>35-24KJ-510 WINDER PLPR START</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>35-24KJ-511 WNDR PLPR STOP PUSHBTN</t>
+          <t>35-24KJ-511 WNDR PLPR STOP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>35-24KJ-544 REEL PULPR STOP</t>
+          <t>35-24KJ-544 REEL PLPR STOP</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7005,6 +7005,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>5001</t>
@@ -7018,6 +7023,11 @@
       <c r="R105" t="inlineStr">
         <is>
           <t>P01</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7634,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>35-24KJ-688 BROKE SCRN START SEQ</t>
+          <t>35-24KJ-688 BROKE SCRNG START SEQ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7686,7 +7696,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>35-24KJ-689 BROKE SCRNG STOP SEQ</t>
+          <t>35-24KJ-689 BROKE SCRN STOP SEQ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8058,7 +8068,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>35-24XS-691 WNDR AREA MCS SIG</t>
+          <t>35-24XS-691 WNDR PLPR MCS SIGNAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8182,7 +8192,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>35-24-008 WINDER PLPR WFL LN</t>
+          <t>35-24-008 WFL LN WINDER PLPR</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8306,7 +8316,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>35-24-012 WFL 15 PROC LN</t>
+          <t>35-24-012 WFL-15 PROC LN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8358,7 +8368,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>35-24-016 WAF 250 HEADER LN</t>
+          <t>35-24-016 WAF 250 DIST HDR</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8410,7 +8420,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>35-24-017 WAF 300 LN</t>
+          <t>35-24-017 WAF LN DN300</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8514,7 +8524,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>35-24-026 WFL 15 GB OL LUB LN</t>
+          <t>35-24-026 WFL 15 GB OL FLSH LN</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8722,7 +8732,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>35-24-042 WFL LN DN15</t>
+          <t>35-24-042 WFL LN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8930,7 +8940,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>35-24-052 WAF 300 DIST HDR LN</t>
+          <t>35-24-052 WAF 300 BROKE DIST HDR</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9034,7 +9044,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>35-24-056 WAF-350 BROKE HDR LN</t>
+          <t>35-24-056 WAF-350 BROKE LN</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9086,7 +9096,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>35-24-061 WFL 15 PROC LN</t>
+          <t>35-24-061 WFL LN DN15</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9138,7 +9148,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>35-24-063 WAF-250 BROKE LN</t>
+          <t>35-24-063 WAF 250 BROKE LN</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9190,7 +9200,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>35-24-068 WFL LN DN15</t>
+          <t>35-24-068 WFL LN BR1</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9242,7 +9252,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>35-24-076 WFL LN 15 GB OL</t>
+          <t>35-24-076 WFL 15 GB OL FL LN</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9294,7 +9304,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>35-24-079 WFL 15 FL LN</t>
+          <t>35-24-079 WFL LN DN15</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9346,7 +9356,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>35-24-080 WFL LN</t>
+          <t>35-24-080 WFL LN 15</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9554,7 +9564,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>35-24-089 WAF-300 LN</t>
+          <t>35-24-089 WAF LN DN300</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9658,7 +9668,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>35-24-098 WAF LN 300</t>
+          <t>35-24-098 WAF-300 PROC LN</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9866,7 +9876,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>35-24-105 WAF-300 PROC LN</t>
+          <t>35-24-105 WAF LN BR1 SHW</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9879,6 +9889,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>5001</t>
@@ -9892,6 +9907,11 @@
       <c r="R157" t="inlineStr">
         <is>
           <t>P01</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9990,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>35-24-109 WAF 500 LN</t>
+          <t>35-24-109 WAF 500 BROKE LN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10022,7 +10042,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>35-24-112 WAF-400 APPROACH FL LN</t>
+          <t>35-24-112 WAF-400 PROC LN</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10230,7 +10250,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>35-24-122 WFL LN BR1</t>
+          <t>35-24-122 WFL SHW LN DN15</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10243,6 +10263,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>5001</t>
@@ -10256,6 +10281,11 @@
       <c r="R164" t="inlineStr">
         <is>
           <t>P01</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>MECH</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10312,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>35-24-123 WFL PROC LN DN15</t>
+          <t>35-24-123 WFL PROC LN</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10542,7 +10572,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>35-24-138 WFL LN</t>
+          <t>35-24-138 WFL 15 FLSH LN</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10698,7 +10728,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>35-24-160 WFL PROC LN</t>
+          <t>35-24-160 WFL LN BR1</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10750,7 +10780,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>35-24-163 WFL LN DN15</t>
+          <t>35-24-163 WFL 15 PROC LN</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -10802,7 +10832,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>35-24-167 PROC LN WFL DN15</t>
+          <t>35-24-167 BROKE PROC LN</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -10958,7 +10988,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>35-24-185 WAF 150 LN</t>
+          <t>35-24-185 WAF 150 BROKE LN</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11062,7 +11092,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>35-24-195 WFL LN</t>
+          <t>35-24-195 WFL LN DN15</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11270,7 +11300,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>35-24-216 CLG WTR RTN LN</t>
+          <t>35-24-216 COOL WTR RTN LN</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11322,7 +11352,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>35-24-219 WFL LN DN15</t>
+          <t>35-24-219 WFL LN 15</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11374,7 +11404,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>35-24-224 WFL LN BR1</t>
+          <t>35-24-224 WFL LN DN15</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11478,7 +11508,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>35-25-072 WAF LN DN350 FM WHT WTR TNK</t>
+          <t>35-25-072 WAF LN DN350</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11491,11 +11521,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>5001</t>
@@ -11509,11 +11534,6 @@
       <c r="R188" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>MECH</t>
         </is>
       </c>
     </row>
